--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:37:59</t>
+          <t>Última actualización: 07:14:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -613,6 +613,214 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07:26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07:27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>53</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>66</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08:26</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>73</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>07:13:31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>92</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -638,7 +846,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:37:59</t>
+          <t>Última actualización: 07:14:17</t>
         </is>
       </c>
     </row>
@@ -660,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,16 +881,100 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:37:59</t>
+          <t>Última actualización: 07:14:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>07:14:17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>07:14:17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>84</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:14:17</t>
+          <t>Última actualización: 08:31:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 25</t>
         </is>
       </c>
     </row>
@@ -821,6 +821,318 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>34</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>41</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>46</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>46</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>54</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>64</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>74</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>85</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>91</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>94</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -833,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,16 +1158,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:14:17</t>
+          <t>Última actualización: 08:31:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>08:30:48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>85</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -868,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -881,14 +1251,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:14:17</t>
+          <t>Última actualización: 08:31:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -975,6 +1345,58 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08:31:08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08:31:28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>57</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:31:29</t>
+          <t>Última actualización: 09:29:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 25</t>
+          <t>Total filas: 36</t>
         </is>
       </c>
     </row>
@@ -1133,6 +1133,292 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>26</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>47</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>56</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>66</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>83</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>86</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>87</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>93</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>96</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1145,7 +1431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,14 +1444,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:31:29</t>
+          <t>Última actualización: 09:29:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -1226,6 +1512,32 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09:28:55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>26</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1238,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,14 +1563,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:31:29</t>
+          <t>Última actualización: 09:29:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -1397,6 +1709,84 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09:29:16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>49</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09:29:36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>61</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09:29:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>74</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:29:36</t>
+          <t>Última actualización: 11:04:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 36</t>
+          <t>Total filas: 44</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1419,214 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>12</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>32</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>34</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>39</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>51</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>87</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>93</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1431,7 +1639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,14 +1652,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:29:36</t>
+          <t>Última actualización: 11:04:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -1538,6 +1746,32 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>11:03:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>32</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1550,7 +1784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1563,14 +1797,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:29:36</t>
+          <t>Última actualización: 11:04:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -1787,6 +2021,32 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>11:03:36</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:04:02</t>
+          <t>Última actualización: 12:14:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 44</t>
+          <t>Total filas: 54</t>
         </is>
       </c>
     </row>
@@ -1627,6 +1627,266 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>17</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>24</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>31</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>33</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>42</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>51</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>62</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>70</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>78</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1639,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,14 +1912,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:04:02</t>
+          <t>Última actualización: 12:14:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -1772,6 +2032,58 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12:13:43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>78</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1784,7 +2096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,14 +2109,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:04:02</t>
+          <t>Última actualización: 12:14:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -2047,6 +2359,58 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12:14:03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>69</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12:14:24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>96</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:14:24</t>
+          <t>Última actualización: 13:12:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 54</t>
+          <t>Total filas: 62</t>
         </is>
       </c>
     </row>
@@ -1887,6 +1887,214 @@
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>45</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>53</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>63</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>66</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>80</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>83</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>13:11:26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>93</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1912,7 +2120,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:14:24</t>
+          <t>Última actualización: 13:12:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2109,14 +2317,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:14:24</t>
+          <t>Última actualización: 13:12:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -2411,6 +2619,32 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13:11:46</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>92</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:12:07</t>
+          <t>Última actualización: 14:16:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 62</t>
+          <t>Total filas: 68</t>
         </is>
       </c>
     </row>
@@ -2095,6 +2095,162 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>47</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>51</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>69</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>81</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>86</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14:15:26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2120,7 +2276,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:12:07</t>
+          <t>Última actualización: 14:16:06</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,14 +2473,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:12:07</t>
+          <t>Última actualización: 14:16:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -2645,6 +2801,32 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14:16:06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>67</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:16:06</t>
+          <t>Última actualización: 15:10:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 68</t>
+          <t>Total filas: 76</t>
         </is>
       </c>
     </row>
@@ -2251,6 +2251,214 @@
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>33</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>43</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>46</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>48</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>55</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>68</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>76</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>15:09:35</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>83_ALUAR</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>86</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2276,7 +2484,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:16:06</t>
+          <t>Última actualización: 15:10:15</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2473,14 +2681,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:16:06</t>
+          <t>Última actualización: 15:10:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -2827,6 +3035,58 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15:09:55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>53</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15:10:15</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:10:15</t>
+          <t>Última actualización: 16:23:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 76</t>
+          <t>Total filas: 85</t>
         </is>
       </c>
     </row>
@@ -2459,6 +2459,240 @@
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>83_ALUAR</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>14</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>30</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>43</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>63</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>70</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>74</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>75</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>93</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2471,7 +2705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,14 +2718,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:10:15</t>
+          <t>Última actualización: 16:23:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -2656,6 +2890,32 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>16:22:26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>93</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2668,7 +2928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2681,14 +2941,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:10:15</t>
+          <t>Última actualización: 16:23:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -3087,6 +3347,32 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>16:22:46</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>61</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:23:07</t>
+          <t>Última actualización: 17:13:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 85</t>
+          <t>Total filas: 92</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2693,188 @@
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>19</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>24</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>51</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>52</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>72</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>82</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>17:12:51</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>84</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2718,7 +2900,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:23:07</t>
+          <t>Última actualización: 17:13:37</t>
         </is>
       </c>
     </row>
@@ -2928,7 +3110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,14 +3123,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:23:07</t>
+          <t>Última actualización: 17:13:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 16</t>
         </is>
       </c>
     </row>
@@ -3373,6 +3555,32 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>17:13:12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:13:37</t>
+          <t>Última actualización: 18:06:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 92</t>
+          <t>Total filas: 103</t>
         </is>
       </c>
     </row>
@@ -2875,6 +2875,292 @@
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>19</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>25</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>29</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>31</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>49</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>54</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>59</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>71</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>71</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>74</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>79</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2887,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2900,14 +3186,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:13:37</t>
+          <t>Última actualización: 18:06:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -3098,6 +3384,58 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>54</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18:06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3110,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3123,14 +3461,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:13:37</t>
+          <t>Última actualización: 18:06:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 16</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -3581,6 +3919,58 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>18:06:22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>39</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>18:06:42</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:06:42</t>
+          <t>Última actualización: 19:06:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 103</t>
+          <t>Total filas: 115</t>
         </is>
       </c>
     </row>
@@ -3161,6 +3161,318 @@
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>26</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>45</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>51</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>56</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>70</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>70</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>91</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>94</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>96</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3173,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3186,14 +3498,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:06:42</t>
+          <t>Última actualización: 19:06:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -3436,6 +3748,84 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>70</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>94</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>19:05:45</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:41</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>96</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3448,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3461,14 +3851,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:06:42</t>
+          <t>Última actualización: 19:06:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 18</t>
+          <t>Total filas: 19</t>
         </is>
       </c>
     </row>
@@ -3971,6 +4361,32 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>19:06:05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>19:47</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>41</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:06:26</t>
+          <t>Última actualización: 20:08:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 115</t>
+          <t>Total filas: 124</t>
         </is>
       </c>
     </row>
@@ -3473,6 +3473,240 @@
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>9</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>50</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>51</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>59</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>59</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>87</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>89</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>21:37</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>90</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>21:42</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>95</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3485,7 +3719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,14 +3732,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:06:26</t>
+          <t>Última actualización: 20:08:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -3826,6 +4060,32 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20:07:28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>59</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3838,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3851,14 +4111,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:06:26</t>
+          <t>Última actualización: 20:08:14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 19</t>
+          <t>Total filas: 21</t>
         </is>
       </c>
     </row>
@@ -4387,6 +4647,58 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20:07:49</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>35</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20:07:49</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>85</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-07-12.xlsx
+++ b/data/horarios-141-2026-07-12.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F129"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:08:14</t>
+          <t>Última actualización: 21:09:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 124</t>
+          <t>Total filas: 133</t>
         </is>
       </c>
     </row>
@@ -3707,6 +3707,240 @@
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>21:16</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>26</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>32</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>21:59</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>50</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>22:07</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>58</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>22:27</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>78</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>88</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>88</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>22:41</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>92</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3719,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3732,14 +3966,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:08:14</t>
+          <t>Última actualización: 21:09:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -4086,6 +4320,32 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>21:09:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>88</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4098,7 +4358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4111,14 +4371,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:08:14</t>
+          <t>Última actualización: 21:09:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 21</t>
+          <t>Total filas: 22</t>
         </is>
       </c>
     </row>
@@ -4699,6 +4959,32 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21:09:42</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>22:09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>60</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
